--- a/MainTop/22.09.2026 МПЕ/Петербург_p2.xlsx
+++ b/MainTop/22.09.2026 МПЕ/Петербург_p2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,19 +481,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Термобирки Юрий</t>
+          <t>Термобирки Маргарита</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Юрий</t>
+          <t>Термобирки Маргарита</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>1296066929</v>
+        <v>2366390031</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -531,25 +531,25 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Термобирки Фёдор</t>
+          <t>Термобирки Ярослав</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Фёдор</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Ярослав</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>1296065955</v>
+        <v>1325161455</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -587,25 +587,25 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Термобирки Надежда</t>
+          <t>Термобирки Мирослава</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Надежда</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Мирослава</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>1302407720</v>
+        <v>1302409296</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -643,25 +643,25 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Термобирки Мухаммад</t>
+          <t>Термобирки Елизавета</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Мухаммад</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Елизавета</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>1296054645</v>
+        <v>1302409438</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -699,25 +699,25 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Термобирки Мирослав</t>
+          <t>Термобирки Богдан</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Мирослав</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Богдан</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>1296069108</v>
+        <v>1296068312</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -755,25 +755,25 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Термобирки Лука</t>
+          <t>Термобирки Алиса</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Лука</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Алиса</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>1296069051</v>
+        <v>1302409496</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -811,25 +811,25 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Термобирки Константин</t>
+          <t>Термобирки Макар</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Константин</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Макар</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>1296065334</v>
+        <v>1296068268</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -867,25 +867,25 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Термобирки Екатерина</t>
+          <t>Термобирки Есения</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Екатерина</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Есения</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>1302407604</v>
+        <v>1302409123</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -923,25 +923,25 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Термобирки Вячеслав</t>
+          <t>Термобирки Дарья</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Вячеслав</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Дарья</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>1296067225</v>
+        <v>1302409355</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -979,25 +979,25 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Термобирки Агния</t>
+          <t>Термобирки Даниил</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Агния</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Даниил</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>1302409086</v>
+        <v>1296053030</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1035,25 +1035,25 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Термобирки Агата</t>
+          <t>Термобирки Вероника</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Агата</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Вероника</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>1302409156</v>
+        <v>1302408998</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1091,25 +1091,25 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Термобирки Любовь</t>
+          <t>Термобирки Алексей</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки в детский сад, именные наклейки, бирки. Любовь</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Алексей</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>1302418750</v>
+        <v>1296065057</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1147,25 +1147,25 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Термобирки Гордей</t>
+          <t>Термобирки Павел</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Термобирки Гордей</t>
+          <t>Термобирки Павел</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>2365502823</v>
+        <v>2365504590</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1203,25 +1203,25 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Термобирки Ясмина</t>
+          <t>Термобирки Николай</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Ясмина</t>
+          <t>Термобирки Николай</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>1302408828</v>
+        <v>2365501207</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1259,25 +1259,25 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Термобирки Юлия</t>
+          <t>Термобирки Сергей</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Юлия</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Сергей</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>1302409546</v>
+        <v>1325163089</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1315,25 +1315,25 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Термобирки Степан</t>
+          <t>Термобирки Кира</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Степан</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Кира</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>1325163507</v>
+        <v>1302409262</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1371,25 +1371,25 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Термобирки Савелий</t>
+          <t>Термобирки Влад</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Савелий</t>
+          <t>Термобирки Влад</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>1296068498</v>
+        <v>2365502926</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1427,25 +1427,25 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Термобирки Савва</t>
+          <t>Термобирки Семён</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Савва</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Семён</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>1296069068</v>
+        <v>1325162457</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1483,25 +1483,25 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Термобирки Ольга</t>
+          <t>Термобирки Анастасия</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Ольга</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Анастасия</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1302408951</v>
+        <v>1302409268</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1539,25 +1539,25 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Термобирки Олег</t>
+          <t>Термобирки Захар</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Олег</t>
+          <t>Термобирки Захар</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1296067164</v>
+        <v>2365502448</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1595,25 +1595,25 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Термобирки Игорь</t>
+          <t>Термобирки Святослав</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Игорь</t>
+          <t>Термобирки Святослав</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>1296066808</v>
+        <v>2365503926</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1651,25 +1651,25 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Термобирки Данил</t>
+          <t>Термобирки Кристина</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Данил</t>
+          <t>Термобирки Кристина</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>1325164077</v>
+        <v>2366379589</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Термобирки Антон</t>
+          <t>Термобирки Евгений</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Антон</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Евгений</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>1296066072</v>
+        <v>1296065971</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1763,25 +1763,25 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Термобирки Виолетта</t>
+          <t>Термобирки Денис</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Термобирки Виолетта</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Денис</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>2366379413</v>
+        <v>1296066026</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1819,25 +1819,25 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Термобирки Вениамин</t>
+          <t>Термобирки Владимир</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Термобирки Вениамин</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Владимир</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>2365503413</v>
+        <v>1325160332</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1875,62 +1875,2358 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Термобирки Александра</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Александра</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1302409458</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Термобирки Аделина</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Аделина</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>4</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1302409334</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Термобирки Григорий</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Термобирки Григорий</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2365501184</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Термобирки Виктор</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Термобирки Виктор</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2365502402</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Термобирки Вера</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Термобирки Вера</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>4</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2366380729</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Термобирки Ульяна</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Термобирки Ульяна</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2366379751</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Термобирки Ника</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Термобирки Ника</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2366379865</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Термобирки Леонид</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Термобирки Леонид</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2365501701</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Термобирки Платон</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Имя Платон</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1296074062</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Термобирки Демид</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Демид</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1296068698</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Термобирки Вадим</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Вадим</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1296067966</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Термобирки Адам</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Адам</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1296068270</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Термобирки Евгения</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Термобирки Евгения</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>3</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2366379688</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Термобирки Давид</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Термобирки Давид</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2365501731</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Термобирки Артур</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Термобирки Артур</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>3</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2365501039</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Термобирки Марьяна</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Термобирки Марьяна</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2366379582</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Термобирки Юрий</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Юрий</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1296066929</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Термобирки Фёдор</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Фёдор</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1296065955</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Термобирки Надежда</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Надежда</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1302407720</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Термобирки Мухаммад</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Мухаммад</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>2</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1296054645</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Термобирки Мирослав</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Мирослав</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1296069108</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Термобирки Лука</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Лука</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1296069051</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Термобирки Константин</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Константин</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>2</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1296065334</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Термобирки Екатерина</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Екатерина</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1302407604</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Термобирки Вячеслав</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Вячеслав</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1296067225</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Термобирки Агния</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Агния</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>2</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1302409086</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Термобирки Агата</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Агата</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>2</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1302409156</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Термобирки Любовь</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Термобирки именные для одежды и маркировки в детский сад, именные наклейки, бирки. Любовь</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>2</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1302418750</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Термобирки Гордей</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Термобирки Гордей</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>2</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2365502823</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Термобирки Ясмина</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Ясмина</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1302408828</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Термобирки Юлия</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Юлия</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1302409546</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Термобирки Степан</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Степан</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1325163507</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Термобирки Савелий</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Савелий</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1296068498</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Термобирки Савва</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Савва</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1296069068</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Термобирки Ольга</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Ольга</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1302408951</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Термобирки Олег</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Олег</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1296067164</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Термобирки Игорь</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Игорь</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1296066808</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Термобирки Данил</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Данил</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1325164077</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Термобирки Антон</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Антон</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1296066072</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Термобирки Виолетта</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Термобирки Виолетта</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="n">
+        <v>2366379413</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Термобирки Вениамин</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Термобирки Вениамин</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="n">
+        <v>2365503413</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>Термобирки Аглая</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>Термобирки Аглая</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C68" t="n">
         <v>1</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D68" t="n">
         <v>2366379897</v>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Дефицитный</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Сортируемый товар</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>4_имена</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>22.09.2026 МПЕ</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Дефицитный</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Сортируемый товар</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>4_имена</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>22.09.2026 МПЕ</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
         <v>1</v>
       </c>
     </row>
